--- a/fock_matrix.xlsx
+++ b/fock_matrix.xlsx
@@ -418,2243 +418,2243 @@
   <sheetData>
     <row r="1">
       <c r="A1" t="n">
-        <v>55.18449938362232</v>
+        <v>-13.9389131768838</v>
       </c>
       <c r="B1" t="n">
-        <v>-1.201238214561132</v>
+        <v>-3.926388842790555</v>
       </c>
       <c r="C1" t="n">
-        <v>-0.818382788584754</v>
+        <v>-2.697560978677542</v>
       </c>
       <c r="D1" t="n">
-        <v>0.4526212491134798</v>
+        <v>1.354430167351911e-16</v>
       </c>
       <c r="E1" t="n">
-        <v>0.146227632944669</v>
+        <v>-2.815349946227869e-16</v>
       </c>
       <c r="F1" t="n">
-        <v>0.4369446463602355</v>
+        <v>-0.02639727642144768</v>
       </c>
       <c r="G1" t="n">
-        <v>0.1340973179705463</v>
+        <v>-4.676118570489135e-18</v>
       </c>
       <c r="H1" t="n">
-        <v>0.07398266543704776</v>
+        <v>-8.803788737159261e-17</v>
       </c>
       <c r="I1" t="n">
-        <v>-0.1186679169995027</v>
+        <v>-0.009843508468678121</v>
       </c>
       <c r="J1" t="n">
-        <v>0.04328927832703032</v>
+        <v>-2.277793963904285e-05</v>
       </c>
       <c r="K1" t="n">
-        <v>0.03724019433344599</v>
+        <v>-6.230826021196089e-05</v>
       </c>
       <c r="L1" t="n">
-        <v>0.05015196270481238</v>
+        <v>-0.01957757246348368</v>
       </c>
       <c r="M1" t="n">
-        <v>-0.01438312874804778</v>
+        <v>3.39784255169843e-17</v>
       </c>
       <c r="N1" t="n">
-        <v>-0.04793011673866256</v>
+        <v>2.552522888200458e-18</v>
       </c>
       <c r="O1" t="n">
-        <v>-0.02078147340424951</v>
+        <v>0.0003428535434659708</v>
       </c>
       <c r="P1" t="n">
-        <v>-0.007514102544864027</v>
+        <v>1.373830487826963e-17</v>
       </c>
       <c r="Q1" t="n">
-        <v>-0.04260902357998272</v>
+        <v>-2.786025309177217e-18</v>
       </c>
       <c r="R1" t="n">
-        <v>-0.1142762458081542</v>
+        <v>0.08399074927681269</v>
       </c>
       <c r="S1" t="n">
-        <v>-0.01738319498265702</v>
+        <v>-0.001029452297107745</v>
       </c>
       <c r="T1" t="n">
-        <v>-0.1123496755649709</v>
+        <v>-0.4485099892615994</v>
       </c>
       <c r="U1" t="n">
-        <v>-0.3805858670024376</v>
+        <v>-0.8853326186362752</v>
       </c>
       <c r="V1" t="n">
-        <v>-0.09857334360723928</v>
+        <v>-4.440135491939364e-17</v>
       </c>
       <c r="W1" t="n">
-        <v>-0.1340388185222633</v>
+        <v>1.162737942979774e-17</v>
       </c>
       <c r="X1" t="n">
-        <v>1.641268049482536</v>
+        <v>0.8781866342360253</v>
       </c>
       <c r="Y1" t="n">
-        <v>0.0561435912350044</v>
+        <v>-2.239209142907633e-17</v>
       </c>
       <c r="Z1" t="n">
-        <v>0.02060803788629982</v>
+        <v>-2.803191920560972e-17</v>
       </c>
       <c r="AA1" t="n">
-        <v>0.3688964258186509</v>
+        <v>1.545025963891933</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>-1.201238214561131</v>
+        <v>-3.926388842790555</v>
       </c>
       <c r="B2" t="n">
-        <v>8.95249120461806</v>
+        <v>0.217890989675031</v>
       </c>
       <c r="C2" t="n">
-        <v>6.373348981687846</v>
+        <v>-0.5132677873979524</v>
       </c>
       <c r="D2" t="n">
-        <v>0.1217100564806427</v>
+        <v>-9.442785887086032e-16</v>
       </c>
       <c r="E2" t="n">
-        <v>0.07308689929308358</v>
+        <v>4.303859865047948e-16</v>
       </c>
       <c r="F2" t="n">
-        <v>6.339559174818699</v>
+        <v>-0.1823484922593758</v>
       </c>
       <c r="G2" t="n">
-        <v>0.103833856217659</v>
+        <v>-8.625690341707752e-16</v>
       </c>
       <c r="H2" t="n">
-        <v>0.09331776170357003</v>
+        <v>7.231842128405798e-17</v>
       </c>
       <c r="I2" t="n">
-        <v>3.129509061228122</v>
+        <v>-0.1425427785019251</v>
       </c>
       <c r="J2" t="n">
-        <v>-0.02872271435768811</v>
+        <v>-6.230826021194799e-05</v>
       </c>
       <c r="K2" t="n">
-        <v>0.04804621410127635</v>
+        <v>-0.002037074100060036</v>
       </c>
       <c r="L2" t="n">
-        <v>0.488379637172573</v>
+        <v>-0.04577124007787286</v>
       </c>
       <c r="M2" t="n">
-        <v>0.02665035994122677</v>
+        <v>-1.575327589092172e-16</v>
       </c>
       <c r="N2" t="n">
-        <v>-0.02049980313820799</v>
+        <v>-2.375682626075259e-17</v>
       </c>
       <c r="O2" t="n">
-        <v>-0.05967270554672911</v>
+        <v>0.001650785517460328</v>
       </c>
       <c r="P2" t="n">
-        <v>-0.3413649377313675</v>
+        <v>6.245707984660922e-17</v>
       </c>
       <c r="Q2" t="n">
-        <v>-0.8196874487134383</v>
+        <v>-9.997634617281538e-17</v>
       </c>
       <c r="R2" t="n">
-        <v>1.720019757756524</v>
+        <v>0.1317120320487972</v>
       </c>
       <c r="S2" t="n">
-        <v>-0.129274310919341</v>
+        <v>-0.1548982083665889</v>
       </c>
       <c r="T2" t="n">
-        <v>0.9557205570893493</v>
+        <v>-0.3658659966946981</v>
       </c>
       <c r="U2" t="n">
-        <v>2.611995783481036</v>
+        <v>-0.3751695949649371</v>
       </c>
       <c r="V2" t="n">
-        <v>0.8434180300837161</v>
+        <v>6.482093157361337e-16</v>
       </c>
       <c r="W2" t="n">
-        <v>0.1356721416658285</v>
+        <v>-5.768805169174925e-16</v>
       </c>
       <c r="X2" t="n">
-        <v>-2.951629545768504</v>
+        <v>0.413808758089591</v>
       </c>
       <c r="Y2" t="n">
-        <v>0.08099713667798128</v>
+        <v>-3.112702011111816e-16</v>
       </c>
       <c r="Z2" t="n">
-        <v>0.08427155490673993</v>
+        <v>6.353841898545101e-17</v>
       </c>
       <c r="AA2" t="n">
-        <v>-3.694736014862673</v>
+        <v>0.3946494718763033</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>-0.8183827885847542</v>
+        <v>-2.697560978677542</v>
       </c>
       <c r="B3" t="n">
-        <v>6.373348981687846</v>
+        <v>-0.5132677873979522</v>
       </c>
       <c r="C3" t="n">
-        <v>6.688486028964796</v>
+        <v>-0.4291537506967799</v>
       </c>
       <c r="D3" t="n">
-        <v>0.1080107079984575</v>
+        <v>1.70925271373994e-15</v>
       </c>
       <c r="E3" t="n">
-        <v>0.0992059998115931</v>
+        <v>-6.53962303214587e-16</v>
       </c>
       <c r="F3" t="n">
-        <v>4.569087176651075</v>
+        <v>-0.2476460458689342</v>
       </c>
       <c r="G3" t="n">
-        <v>0.0568663329187504</v>
+        <v>2.874843147613067e-16</v>
       </c>
       <c r="H3" t="n">
-        <v>0.09852476325808862</v>
+        <v>-2.837392631988946e-16</v>
       </c>
       <c r="I3" t="n">
-        <v>5.634928736893476</v>
+        <v>-0.4428315999746469</v>
       </c>
       <c r="J3" t="n">
-        <v>0.02616149857190184</v>
+        <v>-0.01957757246348371</v>
       </c>
       <c r="K3" t="n">
-        <v>0.4405157380821156</v>
+        <v>-0.04577124007787225</v>
       </c>
       <c r="L3" t="n">
-        <v>1.236144549674822</v>
+        <v>-0.1530478815613011</v>
       </c>
       <c r="M3" t="n">
-        <v>-0.1324986389563614</v>
+        <v>-8.421612013601287e-16</v>
       </c>
       <c r="N3" t="n">
-        <v>-0.1874553085332433</v>
+        <v>7.767699621681544e-17</v>
       </c>
       <c r="O3" t="n">
-        <v>-0.5491754330159049</v>
+        <v>0.05790040587811611</v>
       </c>
       <c r="P3" t="n">
-        <v>0.3890245181911434</v>
+        <v>-2.481454031533025e-16</v>
       </c>
       <c r="Q3" t="n">
-        <v>-0.006243368851932662</v>
+        <v>-3.225396626733715e-17</v>
       </c>
       <c r="R3" t="n">
-        <v>-1.47292328720734</v>
+        <v>0.2993566839521473</v>
       </c>
       <c r="S3" t="n">
-        <v>-0.5278618491030866</v>
+        <v>-0.9000752100896849</v>
       </c>
       <c r="T3" t="n">
-        <v>1.813446858373074</v>
+        <v>-0.5616049500888078</v>
       </c>
       <c r="U3" t="n">
-        <v>0.9339292753502988</v>
+        <v>-0.5080359459677226</v>
       </c>
       <c r="V3" t="n">
-        <v>-0.6841530643549891</v>
+        <v>4.626781688552991e-16</v>
       </c>
       <c r="W3" t="n">
-        <v>0.4648977372355639</v>
+        <v>-3.527770665191413e-16</v>
       </c>
       <c r="X3" t="n">
-        <v>-4.872338936969925</v>
+        <v>0.3427257700439811</v>
       </c>
       <c r="Y3" t="n">
-        <v>-0.1855838638663503</v>
+        <v>-6.783164846643276e-17</v>
       </c>
       <c r="Z3" t="n">
-        <v>0.1735964690947603</v>
+        <v>-3.557803605218208e-17</v>
       </c>
       <c r="AA3" t="n">
-        <v>-3.128439198956056</v>
+        <v>0.2305570657281353</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>0.4526212491134794</v>
+        <v>1.354430167351902e-16</v>
       </c>
       <c r="B4" t="n">
-        <v>0.1217100564806427</v>
+        <v>-9.442785887086091e-16</v>
       </c>
       <c r="C4" t="n">
-        <v>0.1080107079984577</v>
+        <v>1.70925271373994e-15</v>
       </c>
       <c r="D4" t="n">
-        <v>15.57301752116506</v>
+        <v>3.527363555795588</v>
       </c>
       <c r="E4" t="n">
-        <v>-0.0128586842953342</v>
+        <v>1.140283495018604e-15</v>
       </c>
       <c r="F4" t="n">
-        <v>0.05242515380741527</v>
+        <v>-1.407374699646843e-14</v>
       </c>
       <c r="G4" t="n">
-        <v>3.919820115287667</v>
+        <v>0.8452912039115775</v>
       </c>
       <c r="H4" t="n">
-        <v>0.02436939411494165</v>
+        <v>-3.612703095021171e-16</v>
       </c>
       <c r="I4" t="n">
-        <v>0.001574027429646388</v>
+        <v>-1.513161191880386e-15</v>
       </c>
       <c r="J4" t="n">
-        <v>-0.02014829926358701</v>
+        <v>1.137027338551851e-17</v>
       </c>
       <c r="K4" t="n">
-        <v>-1.042983688310378e-05</v>
+        <v>-9.342625539767645e-17</v>
       </c>
       <c r="L4" t="n">
-        <v>0.1258493323505711</v>
+        <v>2.803182876057858e-17</v>
       </c>
       <c r="M4" t="n">
-        <v>0.06518702200442568</v>
+        <v>-0.000157633727060419</v>
       </c>
       <c r="N4" t="n">
-        <v>-0.03239423413150067</v>
+        <v>-3.359394555427065e-17</v>
       </c>
       <c r="O4" t="n">
-        <v>0.002568101092617354</v>
+        <v>-1.122219968897035e-15</v>
       </c>
       <c r="P4" t="n">
-        <v>-0.006729884131357999</v>
+        <v>-0.01283239032860078</v>
       </c>
       <c r="Q4" t="n">
-        <v>-0.08641481815868829</v>
+        <v>-5.093672435854771e-16</v>
       </c>
       <c r="R4" t="n">
-        <v>0.08298628647109868</v>
+        <v>-9.678401045599814e-16</v>
       </c>
       <c r="S4" t="n">
-        <v>-0.009347721661147522</v>
+        <v>7.104945111132761e-16</v>
       </c>
       <c r="T4" t="n">
-        <v>-0.1280226980225189</v>
+        <v>3.247762197431186e-15</v>
       </c>
       <c r="U4" t="n">
-        <v>-0.06995697083609854</v>
+        <v>1.454720075916618e-15</v>
       </c>
       <c r="V4" t="n">
-        <v>-1.623444508206282</v>
+        <v>-0.02193799092565492</v>
       </c>
       <c r="W4" t="n">
-        <v>0.0749727992759153</v>
+        <v>-2.427842827781269e-15</v>
       </c>
       <c r="X4" t="n">
-        <v>-0.04652939776438739</v>
+        <v>-8.394861729787419e-15</v>
       </c>
       <c r="Y4" t="n">
-        <v>-6.885975186475961</v>
+        <v>0.1549630947267702</v>
       </c>
       <c r="Z4" t="n">
-        <v>0.1130759083614428</v>
+        <v>-1.087915168824748e-15</v>
       </c>
       <c r="AA4" t="n">
-        <v>-0.1399306999868982</v>
+        <v>-3.288546787631615e-15</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>0.146227632944669</v>
+        <v>-2.815349946227881e-16</v>
       </c>
       <c r="B5" t="n">
-        <v>0.07308689929308358</v>
+        <v>4.303859865047934e-16</v>
       </c>
       <c r="C5" t="n">
-        <v>0.09920599981159316</v>
+        <v>-6.539623032145832e-16</v>
       </c>
       <c r="D5" t="n">
-        <v>-0.0128586842953342</v>
+        <v>1.140283495018604e-15</v>
       </c>
       <c r="E5" t="n">
-        <v>15.34680331752206</v>
+        <v>3.571735904772265</v>
       </c>
       <c r="F5" t="n">
-        <v>0.01827446424268615</v>
+        <v>5.070753105114011e-15</v>
       </c>
       <c r="G5" t="n">
-        <v>0.02995141294299221</v>
+        <v>3.157797440379332e-16</v>
       </c>
       <c r="H5" t="n">
-        <v>3.954250382726444</v>
+        <v>0.9937784189876107</v>
       </c>
       <c r="I5" t="n">
-        <v>0.00495180921913398</v>
+        <v>1.862977378644034e-15</v>
       </c>
       <c r="J5" t="n">
-        <v>0.03767921008082036</v>
+        <v>-6.117445103472961e-17</v>
       </c>
       <c r="K5" t="n">
-        <v>0.01198441457787414</v>
+        <v>8.717649081767181e-19</v>
       </c>
       <c r="L5" t="n">
-        <v>0.1532876190780578</v>
+        <v>-1.823458690930504e-16</v>
       </c>
       <c r="M5" t="n">
-        <v>-0.01155220301451595</v>
+        <v>2.478403481261462e-16</v>
       </c>
       <c r="N5" t="n">
-        <v>0.04068959479783342</v>
+        <v>-0.0001570574640551021</v>
       </c>
       <c r="O5" t="n">
-        <v>-0.05185808020567099</v>
+        <v>4.184121362838132e-16</v>
       </c>
       <c r="P5" t="n">
-        <v>0.1305030129462645</v>
+        <v>-4.806723473979158e-16</v>
       </c>
       <c r="Q5" t="n">
-        <v>0.3331613594393908</v>
+        <v>-0.01129757344472699</v>
       </c>
       <c r="R5" t="n">
-        <v>-0.04003145009089139</v>
+        <v>5.316011823962527e-16</v>
       </c>
       <c r="S5" t="n">
-        <v>-0.05836804347281761</v>
+        <v>-1.968867188832426e-16</v>
       </c>
       <c r="T5" t="n">
-        <v>-0.3361638313409375</v>
+        <v>-1.031565610655225e-15</v>
       </c>
       <c r="U5" t="n">
-        <v>-0.1414267378950517</v>
+        <v>-3.915137501783903e-16</v>
       </c>
       <c r="V5" t="n">
-        <v>-0.2624065950466219</v>
+        <v>-2.389715389611257e-15</v>
       </c>
       <c r="W5" t="n">
-        <v>-2.065486994334229</v>
+        <v>-0.003817359570537374</v>
       </c>
       <c r="X5" t="n">
-        <v>-0.6532567243171628</v>
+        <v>3.591005271356499e-15</v>
       </c>
       <c r="Y5" t="n">
-        <v>-0.3124212471220639</v>
+        <v>-8.176479522531827e-16</v>
       </c>
       <c r="Z5" t="n">
-        <v>-7.209653834568223</v>
+        <v>0.2045401213949267</v>
       </c>
       <c r="AA5" t="n">
-        <v>-0.4416675868065112</v>
+        <v>2.376062801743562e-15</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>0.4369446463602353</v>
+        <v>-0.02639727642144763</v>
       </c>
       <c r="B6" t="n">
-        <v>6.339559174818699</v>
+        <v>-0.1823484922593757</v>
       </c>
       <c r="C6" t="n">
-        <v>4.569087176651075</v>
+        <v>-0.2476460458689342</v>
       </c>
       <c r="D6" t="n">
-        <v>0.05242515380741525</v>
+        <v>-1.407374699646844e-14</v>
       </c>
       <c r="E6" t="n">
-        <v>0.01827446424268617</v>
+        <v>5.070753105114009e-15</v>
       </c>
       <c r="F6" t="n">
-        <v>16.02744259552757</v>
+        <v>3.658741982478183</v>
       </c>
       <c r="G6" t="n">
-        <v>-0.117836380052036</v>
+        <v>-3.957327920718549e-15</v>
       </c>
       <c r="H6" t="n">
-        <v>-0.04218794387809764</v>
+        <v>1.912393470583124e-15</v>
       </c>
       <c r="I6" t="n">
-        <v>5.270985295017512</v>
+        <v>0.9809709838535751</v>
       </c>
       <c r="J6" t="n">
-        <v>-0.01510401559957807</v>
+        <v>-0.000265163836050582</v>
       </c>
       <c r="K6" t="n">
-        <v>0.002284359395643155</v>
+        <v>-0.0009174596049015336</v>
       </c>
       <c r="L6" t="n">
-        <v>0.3373223685282687</v>
+        <v>-0.05988224482083347</v>
       </c>
       <c r="M6" t="n">
-        <v>-0.01099734247492779</v>
+        <v>7.661647539625372e-16</v>
       </c>
       <c r="N6" t="n">
-        <v>-0.026868861027269</v>
+        <v>3.039577922999708e-18</v>
       </c>
       <c r="O6" t="n">
-        <v>-0.04884595940444765</v>
+        <v>0.01535426023522861</v>
       </c>
       <c r="P6" t="n">
-        <v>0.2152460915051791</v>
+        <v>-1.233844794623437e-16</v>
       </c>
       <c r="Q6" t="n">
-        <v>0.2247589975067503</v>
+        <v>2.956146989154017e-16</v>
       </c>
       <c r="R6" t="n">
-        <v>2.625070266818331</v>
+        <v>0.1820671608501352</v>
       </c>
       <c r="S6" t="n">
-        <v>0.0947529163066311</v>
+        <v>-0.3489153655350307</v>
       </c>
       <c r="T6" t="n">
-        <v>1.32575086431029</v>
+        <v>-0.3953536801162539</v>
       </c>
       <c r="U6" t="n">
-        <v>3.184195409819671</v>
+        <v>-0.2966997846548375</v>
       </c>
       <c r="V6" t="n">
-        <v>-0.3459967911920073</v>
+        <v>-2.841520316624998e-15</v>
       </c>
       <c r="W6" t="n">
-        <v>0.4195138051584595</v>
+        <v>2.12823317796778e-15</v>
       </c>
       <c r="X6" t="n">
-        <v>-0.4803561888961849</v>
+        <v>0.541484987428966</v>
       </c>
       <c r="Y6" t="n">
-        <v>-0.3714016524683519</v>
+        <v>-1.966162560765759e-15</v>
       </c>
       <c r="Z6" t="n">
-        <v>0.17029806960938</v>
+        <v>1.086164613536816e-15</v>
       </c>
       <c r="AA6" t="n">
-        <v>0.93655038481588</v>
+        <v>0.529651551743217</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>0.1340973179705463</v>
+        <v>-4.676118570488777e-18</v>
       </c>
       <c r="B7" t="n">
-        <v>0.103833856217659</v>
+        <v>-8.625690341707729e-16</v>
       </c>
       <c r="C7" t="n">
-        <v>0.0568663329187504</v>
+        <v>2.874843147613061e-16</v>
       </c>
       <c r="D7" t="n">
-        <v>3.919820115287667</v>
+        <v>0.8452912039115775</v>
       </c>
       <c r="E7" t="n">
-        <v>0.02995141294299219</v>
+        <v>3.157797440379332e-16</v>
       </c>
       <c r="F7" t="n">
-        <v>-0.117836380052036</v>
+        <v>-3.957327920718541e-15</v>
       </c>
       <c r="G7" t="n">
-        <v>-32.69183428066827</v>
+        <v>2.510710060485545</v>
       </c>
       <c r="H7" t="n">
-        <v>0.04423089414728601</v>
+        <v>-2.233816682991804e-16</v>
       </c>
       <c r="I7" t="n">
-        <v>-0.04421402633382154</v>
+        <v>4.956609524238502e-17</v>
       </c>
       <c r="J7" t="n">
-        <v>-0.02315524691497832</v>
+        <v>-2.727257329608205e-17</v>
       </c>
       <c r="K7" t="n">
-        <v>0.3255801061502186</v>
+        <v>-1.129571509414952e-16</v>
       </c>
       <c r="L7" t="n">
-        <v>-0.1263729009592731</v>
+        <v>2.953590527484684e-17</v>
       </c>
       <c r="M7" t="n">
-        <v>-0.1472844531923522</v>
+        <v>-0.01819767001717879</v>
       </c>
       <c r="N7" t="n">
-        <v>-0.1116984789471458</v>
+        <v>1.418763668509268e-16</v>
       </c>
       <c r="O7" t="n">
-        <v>-0.01673715769348304</v>
+        <v>-1.173700911047802e-15</v>
       </c>
       <c r="P7" t="n">
-        <v>0.8741554518869886</v>
+        <v>-0.002046171181418734</v>
       </c>
       <c r="Q7" t="n">
-        <v>0.1582014308906845</v>
+        <v>-1.839732069200956e-16</v>
       </c>
       <c r="R7" t="n">
-        <v>0.0660989982664439</v>
+        <v>-6.911487966406049e-16</v>
       </c>
       <c r="S7" t="n">
-        <v>0.073135626049667</v>
+        <v>2.290004478754761e-16</v>
       </c>
       <c r="T7" t="n">
-        <v>0.06837994045107874</v>
+        <v>1.484789642213299e-15</v>
       </c>
       <c r="U7" t="n">
-        <v>0.1410476084206084</v>
+        <v>5.945945227135957e-16</v>
       </c>
       <c r="V7" t="n">
-        <v>5.337001681798523</v>
+        <v>0.1711169882755983</v>
       </c>
       <c r="W7" t="n">
-        <v>0.02977567495134125</v>
+        <v>-1.1538811284587e-15</v>
       </c>
       <c r="X7" t="n">
-        <v>-0.03693212479203911</v>
+        <v>-2.481828301047753e-15</v>
       </c>
       <c r="Y7" t="n">
-        <v>6.486221894468955</v>
+        <v>0.9741593419645682</v>
       </c>
       <c r="Z7" t="n">
-        <v>0.007874901825735955</v>
+        <v>-5.107206273553863e-16</v>
       </c>
       <c r="AA7" t="n">
-        <v>-0.154325305033654</v>
+        <v>-7.422117542355809e-16</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>0.07398266543704782</v>
+        <v>-8.803788737159248e-17</v>
       </c>
       <c r="B8" t="n">
-        <v>0.09331776170357003</v>
+        <v>7.231842128405855e-17</v>
       </c>
       <c r="C8" t="n">
-        <v>0.0985247632580889</v>
+        <v>-2.837392631988953e-16</v>
       </c>
       <c r="D8" t="n">
-        <v>0.02436939411494164</v>
+        <v>-3.612703095021173e-16</v>
       </c>
       <c r="E8" t="n">
-        <v>3.954250382726444</v>
+        <v>0.9937784189876107</v>
       </c>
       <c r="F8" t="n">
-        <v>-0.04218794387809781</v>
+        <v>1.912393470583122e-15</v>
       </c>
       <c r="G8" t="n">
-        <v>0.04423089414728601</v>
+        <v>-2.233816682991804e-16</v>
       </c>
       <c r="H8" t="n">
-        <v>-32.57463986533301</v>
+        <v>2.510512630813733</v>
       </c>
       <c r="I8" t="n">
-        <v>0.0227241454790963</v>
+        <v>6.800170510651974e-16</v>
       </c>
       <c r="J8" t="n">
-        <v>0.01122028636929727</v>
+        <v>-1.302934076780943e-17</v>
       </c>
       <c r="K8" t="n">
-        <v>0.7159033823745661</v>
+        <v>2.069300806596466e-16</v>
       </c>
       <c r="L8" t="n">
-        <v>-0.5710402794724226</v>
+        <v>3.016616565043583e-17</v>
       </c>
       <c r="M8" t="n">
-        <v>0.2730272557697068</v>
+        <v>-5.117359406604896e-16</v>
       </c>
       <c r="N8" t="n">
-        <v>0.173504781518794</v>
+        <v>-0.0181963784096797</v>
       </c>
       <c r="O8" t="n">
-        <v>0.4013542245627923</v>
+        <v>6.609435577485421e-16</v>
       </c>
       <c r="P8" t="n">
-        <v>0.04114849708239793</v>
+        <v>-4.885146641146722e-16</v>
       </c>
       <c r="Q8" t="n">
-        <v>0.5880521153089078</v>
+        <v>-0.002103379677665012</v>
       </c>
       <c r="R8" t="n">
-        <v>1.030240134340809</v>
+        <v>4.268651311508884e-16</v>
       </c>
       <c r="S8" t="n">
-        <v>-0.002490278289474556</v>
+        <v>-8.24863212068459e-17</v>
       </c>
       <c r="T8" t="n">
-        <v>0.4089003556476137</v>
+        <v>-4.055425597086786e-16</v>
       </c>
       <c r="U8" t="n">
-        <v>0.4523065077777619</v>
+        <v>-1.246074753346391e-16</v>
       </c>
       <c r="V8" t="n">
-        <v>-0.08356384241569548</v>
+        <v>-1.317828186369678e-15</v>
       </c>
       <c r="W8" t="n">
-        <v>5.231435240104406</v>
+        <v>0.1709153137206992</v>
       </c>
       <c r="X8" t="n">
-        <v>0.2853037065911365</v>
+        <v>8.898295177029086e-16</v>
       </c>
       <c r="Y8" t="n">
-        <v>-0.1362071837957134</v>
+        <v>-6.250833465720376e-16</v>
       </c>
       <c r="Z8" t="n">
-        <v>6.630293134008576</v>
+        <v>0.9740993718618542</v>
       </c>
       <c r="AA8" t="n">
-        <v>0.9842143876026266</v>
+        <v>8.54908327031768e-16</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>-0.1186679169995026</v>
+        <v>-0.00984350846867812</v>
       </c>
       <c r="B9" t="n">
-        <v>3.129509061228122</v>
+        <v>-0.1425427785019251</v>
       </c>
       <c r="C9" t="n">
-        <v>5.634928736893475</v>
+        <v>-0.4428315999746469</v>
       </c>
       <c r="D9" t="n">
-        <v>0.0015740274296464</v>
+        <v>-1.513161191880391e-15</v>
       </c>
       <c r="E9" t="n">
-        <v>0.004951809219133992</v>
+        <v>1.862977378644034e-15</v>
       </c>
       <c r="F9" t="n">
-        <v>5.270985295017513</v>
+        <v>0.980970983853575</v>
       </c>
       <c r="G9" t="n">
-        <v>-0.04421402633382159</v>
+        <v>4.956609524238483e-17</v>
       </c>
       <c r="H9" t="n">
-        <v>0.02272414547909629</v>
+        <v>6.800170510651975e-16</v>
       </c>
       <c r="I9" t="n">
-        <v>-39.72379262336587</v>
+        <v>1.889784629673521</v>
       </c>
       <c r="J9" t="n">
-        <v>0.1399333959901065</v>
+        <v>-0.08375259002425961</v>
       </c>
       <c r="K9" t="n">
-        <v>-1.63290802553283</v>
+        <v>-0.1267033434721536</v>
       </c>
       <c r="L9" t="n">
-        <v>1.113417263293818</v>
+        <v>-0.3045692291008574</v>
       </c>
       <c r="M9" t="n">
-        <v>-0.1649554190616011</v>
+        <v>-1.050252934013578e-15</v>
       </c>
       <c r="N9" t="n">
-        <v>0.1632421619841654</v>
+        <v>2.821195223598736e-16</v>
       </c>
       <c r="O9" t="n">
-        <v>2.037512427300246</v>
+        <v>0.1554317950379212</v>
       </c>
       <c r="P9" t="n">
-        <v>0.3927301402936784</v>
+        <v>-5.051104442888832e-16</v>
       </c>
       <c r="Q9" t="n">
-        <v>-0.6586422515907684</v>
+        <v>1.814784305912585e-16</v>
       </c>
       <c r="R9" t="n">
-        <v>-9.343772687516585</v>
+        <v>0.5511885150207049</v>
       </c>
       <c r="S9" t="n">
-        <v>2.491636785242362</v>
+        <v>-1.934464379029403</v>
       </c>
       <c r="T9" t="n">
-        <v>7.785166573679937</v>
+        <v>-0.7339825201268612</v>
       </c>
       <c r="U9" t="n">
-        <v>6.813390689025391</v>
+        <v>-0.6219459620189018</v>
       </c>
       <c r="V9" t="n">
-        <v>-0.447332269023948</v>
+        <v>-8.624618311010118e-16</v>
       </c>
       <c r="W9" t="n">
-        <v>0.3863315273073227</v>
+        <v>8.57354383614665e-16</v>
       </c>
       <c r="X9" t="n">
-        <v>-2.698014891868742</v>
+        <v>0.3870988161753057</v>
       </c>
       <c r="Y9" t="n">
-        <v>-0.4430089848808493</v>
+        <v>-4.021546321404038e-16</v>
       </c>
       <c r="Z9" t="n">
-        <v>0.5422915964793452</v>
+        <v>3.450208516951406e-16</v>
       </c>
       <c r="AA9" t="n">
-        <v>-1.991259003350291</v>
+        <v>0.9272706486401135</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>0.04328927832703033</v>
+        <v>-2.277793963904295e-05</v>
       </c>
       <c r="B10" t="n">
-        <v>-0.02872271435768814</v>
+        <v>-6.230826021194593e-05</v>
       </c>
       <c r="C10" t="n">
-        <v>0.02616149857190186</v>
+        <v>-0.01957757246348371</v>
       </c>
       <c r="D10" t="n">
-        <v>-0.020148299263587</v>
+        <v>1.137027338551817e-17</v>
       </c>
       <c r="E10" t="n">
-        <v>0.03767921008082038</v>
+        <v>-6.117445103472972e-17</v>
       </c>
       <c r="F10" t="n">
-        <v>-0.0151040155995781</v>
+        <v>-0.0002651638360505821</v>
       </c>
       <c r="G10" t="n">
-        <v>-0.0231552469149783</v>
+        <v>-2.727257329608203e-17</v>
       </c>
       <c r="H10" t="n">
-        <v>0.01122028636929727</v>
+        <v>-1.302934076780944e-17</v>
       </c>
       <c r="I10" t="n">
-        <v>0.1399333959901065</v>
+        <v>-0.08375259002425962</v>
       </c>
       <c r="J10" t="n">
-        <v>55.24487596095116</v>
+        <v>-13.95225599594582</v>
       </c>
       <c r="K10" t="n">
-        <v>-1.01097840451989</v>
+        <v>-3.929521380951683</v>
       </c>
       <c r="L10" t="n">
-        <v>-0.6410796817909166</v>
+        <v>-2.69980020393878</v>
       </c>
       <c r="M10" t="n">
-        <v>-0.07692582381210565</v>
+        <v>-3.369620129559019e-16</v>
       </c>
       <c r="N10" t="n">
-        <v>0.1076378609332797</v>
+        <v>7.285592988543995e-17</v>
       </c>
       <c r="O10" t="n">
-        <v>-0.5950405314480431</v>
+        <v>0.02804265183843993</v>
       </c>
       <c r="P10" t="n">
-        <v>-0.07108514396141527</v>
+        <v>2.163864265845953e-17</v>
       </c>
       <c r="Q10" t="n">
-        <v>0.16201935484581</v>
+        <v>-1.183715604822857e-17</v>
       </c>
       <c r="R10" t="n">
-        <v>0.06447963069280009</v>
+        <v>0.0100653985702153</v>
       </c>
       <c r="S10" t="n">
-        <v>0.03480377591465637</v>
+        <v>-0.00102962340408738</v>
       </c>
       <c r="T10" t="n">
-        <v>-0.0301108637949353</v>
+        <v>-0.448902598354377</v>
       </c>
       <c r="U10" t="n">
-        <v>-0.2836013890410759</v>
+        <v>-0.886080461457566</v>
       </c>
       <c r="V10" t="n">
-        <v>0.1161924861022333</v>
+        <v>2.834107188960351e-16</v>
       </c>
       <c r="W10" t="n">
-        <v>0.1936123998028958</v>
+        <v>-2.055058311315414e-16</v>
       </c>
       <c r="X10" t="n">
-        <v>-1.56192786638408</v>
+        <v>-0.8789230654611183</v>
       </c>
       <c r="Y10" t="n">
-        <v>-0.109882567019687</v>
+        <v>8.487132748131886e-17</v>
       </c>
       <c r="Z10" t="n">
-        <v>0.01192236380962837</v>
+        <v>-6.023827293227171e-17</v>
       </c>
       <c r="AA10" t="n">
-        <v>-0.03876353897098994</v>
+        <v>-1.546277333727295</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>0.03724019433344607</v>
+        <v>-6.230826021196013e-05</v>
       </c>
       <c r="B11" t="n">
-        <v>0.04804621410127635</v>
+        <v>-0.002037074100060028</v>
       </c>
       <c r="C11" t="n">
-        <v>0.440515738082116</v>
+        <v>-0.04577124007787226</v>
       </c>
       <c r="D11" t="n">
-        <v>-1.042983688310031e-05</v>
+        <v>-9.342625539767428e-17</v>
       </c>
       <c r="E11" t="n">
-        <v>0.01198441457787412</v>
+        <v>8.717649081747891e-19</v>
       </c>
       <c r="F11" t="n">
-        <v>0.002284359395643238</v>
+        <v>-0.0009174596049015321</v>
       </c>
       <c r="G11" t="n">
-        <v>0.3255801061502185</v>
+        <v>-1.129571509414954e-16</v>
       </c>
       <c r="H11" t="n">
-        <v>0.7159033823745662</v>
+        <v>2.069300806596464e-16</v>
       </c>
       <c r="I11" t="n">
-        <v>-1.63290802553283</v>
+        <v>-0.1267033434721536</v>
       </c>
       <c r="J11" t="n">
-        <v>-1.01097840451989</v>
+        <v>-3.929521380951684</v>
       </c>
       <c r="K11" t="n">
-        <v>7.925195864662754</v>
+        <v>0.2044272075953286</v>
       </c>
       <c r="L11" t="n">
-        <v>5.854368211625602</v>
+        <v>-0.5235196805689166</v>
       </c>
       <c r="M11" t="n">
-        <v>0.1190286776524328</v>
+        <v>2.177941710903223e-15</v>
       </c>
       <c r="N11" t="n">
-        <v>0.00706560709110042</v>
+        <v>-7.683914668691754e-16</v>
       </c>
       <c r="O11" t="n">
-        <v>-5.323188358079372</v>
+        <v>0.1933634701993213</v>
       </c>
       <c r="P11" t="n">
-        <v>0.04607537279012264</v>
+        <v>3.347808366891393e-16</v>
       </c>
       <c r="Q11" t="n">
-        <v>0.04977086925797988</v>
+        <v>-2.011854940651165e-16</v>
       </c>
       <c r="R11" t="n">
-        <v>-2.625747489057233</v>
+        <v>0.1495582194145315</v>
       </c>
       <c r="S11" t="n">
-        <v>0.0198009548809519</v>
+        <v>-0.1556929556002188</v>
       </c>
       <c r="T11" t="n">
-        <v>1.255340769714345</v>
+        <v>-0.3706875798819583</v>
       </c>
       <c r="U11" t="n">
-        <v>2.697047871871722</v>
+        <v>-0.3804397745048268</v>
       </c>
       <c r="V11" t="n">
-        <v>-0.4836004603135649</v>
+        <v>-2.505227853843419e-15</v>
       </c>
       <c r="W11" t="n">
-        <v>-0.6745133220491555</v>
+        <v>1.304562247575277e-15</v>
       </c>
       <c r="X11" t="n">
-        <v>2.226334790996348</v>
+        <v>-0.4186609515153875</v>
       </c>
       <c r="Y11" t="n">
-        <v>-0.1188825976930062</v>
+        <v>-6.381718564684414e-16</v>
       </c>
       <c r="Z11" t="n">
-        <v>-0.3757052065289835</v>
+        <v>-6.491623686141709e-18</v>
       </c>
       <c r="AA11" t="n">
-        <v>3.367259288612123</v>
+        <v>-0.3995492601013803</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>0.05015196270481233</v>
+        <v>-0.01957757246348368</v>
       </c>
       <c r="B12" t="n">
-        <v>0.4883796371725726</v>
+        <v>-0.04577124007787287</v>
       </c>
       <c r="C12" t="n">
-        <v>1.236144549674821</v>
+        <v>-0.1530478815613011</v>
       </c>
       <c r="D12" t="n">
-        <v>0.1258493323505711</v>
+        <v>2.803182876057982e-17</v>
       </c>
       <c r="E12" t="n">
-        <v>0.1532876190780578</v>
+        <v>-1.823458690930494e-16</v>
       </c>
       <c r="F12" t="n">
-        <v>0.3373223685282686</v>
+        <v>-0.05988224482083347</v>
       </c>
       <c r="G12" t="n">
-        <v>-0.1263729009592731</v>
+        <v>2.953590527484585e-17</v>
       </c>
       <c r="H12" t="n">
-        <v>-0.5710402794724226</v>
+        <v>3.016616565043651e-17</v>
       </c>
       <c r="I12" t="n">
-        <v>1.113417263293819</v>
+        <v>-0.3045692291008574</v>
       </c>
       <c r="J12" t="n">
-        <v>-0.6410796817909163</v>
+        <v>-2.69980020393878</v>
       </c>
       <c r="K12" t="n">
-        <v>5.854368211625604</v>
+        <v>-0.5235196805689165</v>
       </c>
       <c r="L12" t="n">
-        <v>6.641356389597132</v>
+        <v>-0.4422452982433335</v>
       </c>
       <c r="M12" t="n">
-        <v>0.09737800460879353</v>
+        <v>8.314489829454551e-16</v>
       </c>
       <c r="N12" t="n">
-        <v>-0.05022453679074389</v>
+        <v>-2.246349166833899e-16</v>
       </c>
       <c r="O12" t="n">
-        <v>-3.94050733838921</v>
+        <v>0.2580662118769882</v>
       </c>
       <c r="P12" t="n">
-        <v>0.006442139959555643</v>
+        <v>1.354245747056415e-16</v>
       </c>
       <c r="Q12" t="n">
-        <v>0.00110899242197926</v>
+        <v>-1.147140928180091e-16</v>
       </c>
       <c r="R12" t="n">
-        <v>-2.544508886912311</v>
+        <v>0.4602673838020144</v>
       </c>
       <c r="S12" t="n">
-        <v>-0.4793215894898792</v>
+        <v>-0.9068774117505555</v>
       </c>
       <c r="T12" t="n">
-        <v>1.338077009442698</v>
+        <v>-0.577525469621741</v>
       </c>
       <c r="U12" t="n">
-        <v>0.6268489586541655</v>
+        <v>-0.5216323966291417</v>
       </c>
       <c r="V12" t="n">
-        <v>0.02808600165576955</v>
+        <v>-1.10487021022716e-15</v>
       </c>
       <c r="W12" t="n">
-        <v>0.1271902983050405</v>
+        <v>5.160023992588327e-16</v>
       </c>
       <c r="X12" t="n">
-        <v>5.807717669033385</v>
+        <v>-0.3380487766738053</v>
       </c>
       <c r="Y12" t="n">
-        <v>-0.0003867658997993573</v>
+        <v>-2.41573570985293e-16</v>
       </c>
       <c r="Z12" t="n">
-        <v>-0.04394511397550993</v>
+        <v>-1.367594521940176e-16</v>
       </c>
       <c r="AA12" t="n">
-        <v>3.604980515111603</v>
+        <v>-0.2302815346541631</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>-0.01438312874804778</v>
+        <v>3.397842551698439e-17</v>
       </c>
       <c r="B13" t="n">
-        <v>0.02665035994122673</v>
+        <v>-1.57532758909217e-16</v>
       </c>
       <c r="C13" t="n">
-        <v>-0.1324986389563613</v>
+        <v>-8.421612013601298e-16</v>
       </c>
       <c r="D13" t="n">
-        <v>0.06518702200442568</v>
+        <v>-0.000157633727060421</v>
       </c>
       <c r="E13" t="n">
-        <v>-0.01155220301451596</v>
+        <v>2.478403481261463e-16</v>
       </c>
       <c r="F13" t="n">
-        <v>-0.01099734247492778</v>
+        <v>7.661647539625363e-16</v>
       </c>
       <c r="G13" t="n">
-        <v>-0.1472844531923522</v>
+        <v>-0.01819767001717879</v>
       </c>
       <c r="H13" t="n">
-        <v>0.2730272557697067</v>
+        <v>-5.117359406604894e-16</v>
       </c>
       <c r="I13" t="n">
-        <v>-0.1649554190616011</v>
+        <v>-1.050252934013578e-15</v>
       </c>
       <c r="J13" t="n">
-        <v>-0.07692582381210565</v>
+        <v>-3.369620129559043e-16</v>
       </c>
       <c r="K13" t="n">
-        <v>0.1190286776524328</v>
+        <v>2.177941710903221e-15</v>
       </c>
       <c r="L13" t="n">
-        <v>0.09737800460879351</v>
+        <v>8.314489829454543e-16</v>
       </c>
       <c r="M13" t="n">
-        <v>17.0453349999324</v>
+        <v>3.534617372466488</v>
       </c>
       <c r="N13" t="n">
-        <v>0.1204601890429589</v>
+        <v>1.319638375443824e-15</v>
       </c>
       <c r="O13" t="n">
-        <v>-0.01896619295663794</v>
+        <v>1.048098519045619e-14</v>
       </c>
       <c r="P13" t="n">
-        <v>2.753453046695021</v>
+        <v>0.8595657659756692</v>
       </c>
       <c r="Q13" t="n">
-        <v>0.04213025238886331</v>
+        <v>-6.016294178300968e-16</v>
       </c>
       <c r="R13" t="n">
-        <v>-0.04349082956845973</v>
+        <v>8.807983829848874e-15</v>
       </c>
       <c r="S13" t="n">
-        <v>0.07073476385981425</v>
+        <v>2.584785212029677e-16</v>
       </c>
       <c r="T13" t="n">
-        <v>0.1571351373104556</v>
+        <v>-1.744364857432544e-15</v>
       </c>
       <c r="U13" t="n">
-        <v>0.2658634213724857</v>
+        <v>-1.023035054805016e-15</v>
       </c>
       <c r="V13" t="n">
-        <v>-1.693080574389559</v>
+        <v>-0.01792151295006109</v>
       </c>
       <c r="W13" t="n">
-        <v>-0.2170838249720593</v>
+        <v>-2.552431707371661e-15</v>
       </c>
       <c r="X13" t="n">
-        <v>0.4431876117659879</v>
+        <v>5.121282968712052e-15</v>
       </c>
       <c r="Y13" t="n">
-        <v>-7.003061544246973</v>
+        <v>0.1614379705728501</v>
       </c>
       <c r="Z13" t="n">
-        <v>-0.3368017147838947</v>
+        <v>-1.136722225820409e-15</v>
       </c>
       <c r="AA13" t="n">
-        <v>0.01935864227917947</v>
+        <v>4.91108500308062e-15</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>-0.04793011673866257</v>
+        <v>2.552522888200456e-18</v>
       </c>
       <c r="B14" t="n">
-        <v>-0.02049980313820794</v>
+        <v>-2.375682626075278e-17</v>
       </c>
       <c r="C14" t="n">
-        <v>-0.1874553085332433</v>
+        <v>7.767699621681552e-17</v>
       </c>
       <c r="D14" t="n">
-        <v>-0.03239423413150068</v>
+        <v>-3.359394555427063e-17</v>
       </c>
       <c r="E14" t="n">
-        <v>0.04068959479783341</v>
+        <v>-0.0001570574640551039</v>
       </c>
       <c r="F14" t="n">
-        <v>-0.026868861027269</v>
+        <v>3.039577922999701e-18</v>
       </c>
       <c r="G14" t="n">
-        <v>-0.1116984789471458</v>
+        <v>1.418763668509268e-16</v>
       </c>
       <c r="H14" t="n">
-        <v>0.173504781518794</v>
+        <v>-0.01819637840967971</v>
       </c>
       <c r="I14" t="n">
-        <v>0.1632421619841654</v>
+        <v>2.821195223598735e-16</v>
       </c>
       <c r="J14" t="n">
-        <v>0.1076378609332797</v>
+        <v>7.285592988543967e-17</v>
       </c>
       <c r="K14" t="n">
-        <v>0.007065607091100476</v>
+        <v>-7.683914668691756e-16</v>
       </c>
       <c r="L14" t="n">
-        <v>-0.05022453679074397</v>
+        <v>-2.246349166833906e-16</v>
       </c>
       <c r="M14" t="n">
-        <v>0.1204601890429589</v>
+        <v>1.319638375443824e-15</v>
       </c>
       <c r="N14" t="n">
-        <v>17.30813071452934</v>
+        <v>3.578891722850833</v>
       </c>
       <c r="O14" t="n">
-        <v>-0.1223067705290536</v>
+        <v>4.834494402823264e-16</v>
       </c>
       <c r="P14" t="n">
-        <v>0.1415541976626938</v>
+        <v>3.497700990479528e-16</v>
       </c>
       <c r="Q14" t="n">
-        <v>2.799247588640772</v>
+        <v>1.008050734914647</v>
       </c>
       <c r="R14" t="n">
-        <v>0.00484654616929211</v>
+        <v>-1.184101487146061e-15</v>
       </c>
       <c r="S14" t="n">
-        <v>-0.0380367428542126</v>
+        <v>5.466642736909423e-17</v>
       </c>
       <c r="T14" t="n">
-        <v>-0.4230659291664233</v>
+        <v>8.399154813701662e-16</v>
       </c>
       <c r="U14" t="n">
-        <v>0.03332009187427507</v>
+        <v>3.427854697205191e-16</v>
       </c>
       <c r="V14" t="n">
-        <v>0.2443410447201789</v>
+        <v>2.703582589645091e-16</v>
       </c>
       <c r="W14" t="n">
-        <v>-1.833428106827623</v>
+        <v>0.0001944904163663774</v>
       </c>
       <c r="X14" t="n">
-        <v>-0.4495950769629764</v>
+        <v>5.426631478700654e-16</v>
       </c>
       <c r="Y14" t="n">
-        <v>0.1733919514998904</v>
+        <v>1.815542495463897e-16</v>
       </c>
       <c r="Z14" t="n">
-        <v>-7.229748159878575</v>
+        <v>0.2110164439067542</v>
       </c>
       <c r="AA14" t="n">
-        <v>-0.1790713917819428</v>
+        <v>-4.463615971472972e-16</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>-0.02078147340424951</v>
+        <v>0.0003428535434659678</v>
       </c>
       <c r="B15" t="n">
-        <v>-0.05967270554672909</v>
+        <v>0.001650785517460344</v>
       </c>
       <c r="C15" t="n">
-        <v>-0.5491754330159049</v>
+        <v>0.05790040587811611</v>
       </c>
       <c r="D15" t="n">
-        <v>0.002568101092617355</v>
+        <v>-1.122219968897037e-15</v>
       </c>
       <c r="E15" t="n">
-        <v>-0.05185808020567101</v>
+        <v>4.184121362838133e-16</v>
       </c>
       <c r="F15" t="n">
-        <v>-0.04884595940444762</v>
+        <v>0.01535426023522862</v>
       </c>
       <c r="G15" t="n">
-        <v>-0.01673715769348305</v>
+        <v>-1.173700911047803e-15</v>
       </c>
       <c r="H15" t="n">
-        <v>0.4013542245627924</v>
+        <v>6.609435577485417e-16</v>
       </c>
       <c r="I15" t="n">
-        <v>2.037512427300246</v>
+        <v>0.1554317950379212</v>
       </c>
       <c r="J15" t="n">
-        <v>-0.5950405314480431</v>
+        <v>0.02804265183843987</v>
       </c>
       <c r="K15" t="n">
-        <v>-5.323188358079372</v>
+        <v>0.1933634701993212</v>
       </c>
       <c r="L15" t="n">
-        <v>-3.94050733838921</v>
+        <v>0.2580662118769882</v>
       </c>
       <c r="M15" t="n">
-        <v>-0.01896619295663796</v>
+        <v>1.048098519045618e-14</v>
       </c>
       <c r="N15" t="n">
-        <v>-0.1223067705290536</v>
+        <v>4.83449440282326e-16</v>
       </c>
       <c r="O15" t="n">
-        <v>17.67482328643908</v>
+        <v>3.667916564795687</v>
       </c>
       <c r="P15" t="n">
-        <v>-0.06297290253979139</v>
+        <v>1.709340736811642e-15</v>
       </c>
       <c r="Q15" t="n">
-        <v>-0.06136687677283039</v>
+        <v>9.370556832228718e-16</v>
       </c>
       <c r="R15" t="n">
-        <v>3.172796873428037</v>
+        <v>0.9973798097464642</v>
       </c>
       <c r="S15" t="n">
-        <v>-0.1237535077874991</v>
+        <v>0.3507274610483516</v>
       </c>
       <c r="T15" t="n">
-        <v>-0.7960451429673899</v>
+        <v>0.4045123829044743</v>
       </c>
       <c r="U15" t="n">
-        <v>-1.899240216894777</v>
+        <v>0.3048297340942763</v>
       </c>
       <c r="V15" t="n">
-        <v>-0.006553005688697086</v>
+        <v>-5.407272537082234e-15</v>
       </c>
       <c r="W15" t="n">
-        <v>-0.4094931920805067</v>
+        <v>3.76880785456763e-15</v>
       </c>
       <c r="X15" t="n">
-        <v>1.746614109458255</v>
+        <v>0.5585835805140056</v>
       </c>
       <c r="Y15" t="n">
-        <v>-0.1821002273832631</v>
+        <v>-1.675945387654658e-15</v>
       </c>
       <c r="Z15" t="n">
-        <v>-0.3732416647863951</v>
+        <v>1.490196332373673e-15</v>
       </c>
       <c r="AA15" t="n">
-        <v>2.385010128216951</v>
+        <v>0.5479858710481769</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>-0.007514102544864022</v>
+        <v>1.373830487826967e-17</v>
       </c>
       <c r="B16" t="n">
-        <v>-0.3413649377313676</v>
+        <v>6.245707984660764e-17</v>
       </c>
       <c r="C16" t="n">
-        <v>0.3890245181911434</v>
+        <v>-2.48145403153303e-16</v>
       </c>
       <c r="D16" t="n">
-        <v>-0.00672988413135811</v>
+        <v>-0.01283239032860078</v>
       </c>
       <c r="E16" t="n">
-        <v>0.1305030129462645</v>
+        <v>-4.806723473979157e-16</v>
       </c>
       <c r="F16" t="n">
-        <v>0.2152460915051792</v>
+        <v>-1.233844794623439e-16</v>
       </c>
       <c r="G16" t="n">
-        <v>0.8741554518869887</v>
+        <v>-0.002046171181418734</v>
       </c>
       <c r="H16" t="n">
-        <v>0.04114849708239791</v>
+        <v>-4.885146641146723e-16</v>
       </c>
       <c r="I16" t="n">
-        <v>0.3927301402936786</v>
+        <v>-5.051104442888827e-16</v>
       </c>
       <c r="J16" t="n">
-        <v>-0.07108514396141527</v>
+        <v>2.163864265845847e-17</v>
       </c>
       <c r="K16" t="n">
-        <v>0.04607537279012261</v>
+        <v>3.347808366891383e-16</v>
       </c>
       <c r="L16" t="n">
-        <v>0.006442139959555532</v>
+        <v>1.354245747056448e-16</v>
       </c>
       <c r="M16" t="n">
-        <v>2.753453046695021</v>
+        <v>0.8595657659756692</v>
       </c>
       <c r="N16" t="n">
-        <v>0.1415541976626938</v>
+        <v>3.49770099047953e-16</v>
       </c>
       <c r="O16" t="n">
-        <v>-0.06297290253979136</v>
+        <v>1.709340736811642e-15</v>
       </c>
       <c r="P16" t="n">
-        <v>-34.32218500426923</v>
+        <v>2.604307947386128</v>
       </c>
       <c r="Q16" t="n">
-        <v>0.04370180008433452</v>
+        <v>-3.405458763754786e-16</v>
       </c>
       <c r="R16" t="n">
-        <v>-0.0488388921586144</v>
+        <v>2.336615803103468e-15</v>
       </c>
       <c r="S16" t="n">
-        <v>-0.04818092515576727</v>
+        <v>1.697406369097807e-16</v>
       </c>
       <c r="T16" t="n">
-        <v>-0.1169252807846761</v>
+        <v>-3.039397228271346e-16</v>
       </c>
       <c r="U16" t="n">
-        <v>-0.1713676256734851</v>
+        <v>-2.520063900823526e-16</v>
       </c>
       <c r="V16" t="n">
-        <v>5.252382510381475</v>
+        <v>0.2279949242537498</v>
       </c>
       <c r="W16" t="n">
-        <v>-0.1080358716043331</v>
+        <v>-1.313533409624755e-15</v>
       </c>
       <c r="X16" t="n">
-        <v>0.4499433205242608</v>
+        <v>2.899685644282149e-15</v>
       </c>
       <c r="Y16" t="n">
-        <v>6.123235008855699</v>
+        <v>1.098524600347202</v>
       </c>
       <c r="Z16" t="n">
-        <v>-0.1272072262122085</v>
+        <v>-6.524779255080973e-16</v>
       </c>
       <c r="AA16" t="n">
-        <v>0.5604429974200316</v>
+        <v>1.798254687057362e-15</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>-0.04260902357998274</v>
+        <v>-2.786025309177214e-18</v>
       </c>
       <c r="B17" t="n">
-        <v>-0.8196874487134383</v>
+        <v>-9.99763461728153e-17</v>
       </c>
       <c r="C17" t="n">
-        <v>-0.006243368851932496</v>
+        <v>-3.225396626733719e-17</v>
       </c>
       <c r="D17" t="n">
-        <v>-0.08641481815868828</v>
+        <v>-5.093672435854774e-16</v>
       </c>
       <c r="E17" t="n">
-        <v>0.3331613594393906</v>
+        <v>-0.01129757344472699</v>
       </c>
       <c r="F17" t="n">
-        <v>0.2247589975067505</v>
+        <v>2.956146989154016e-16</v>
       </c>
       <c r="G17" t="n">
-        <v>0.1582014308906845</v>
+        <v>-1.839732069200956e-16</v>
       </c>
       <c r="H17" t="n">
-        <v>0.5880521153089078</v>
+        <v>-0.002103379677665013</v>
       </c>
       <c r="I17" t="n">
-        <v>-0.6586422515907681</v>
+        <v>1.814784305912586e-16</v>
       </c>
       <c r="J17" t="n">
-        <v>0.16201935484581</v>
+        <v>-1.183715604822855e-17</v>
       </c>
       <c r="K17" t="n">
-        <v>0.04977086925797977</v>
+        <v>-2.011854940651164e-16</v>
       </c>
       <c r="L17" t="n">
-        <v>0.00110899242197926</v>
+        <v>-1.147140928180092e-16</v>
       </c>
       <c r="M17" t="n">
-        <v>0.04213025238886328</v>
+        <v>-6.016294178300967e-16</v>
       </c>
       <c r="N17" t="n">
-        <v>2.799247588640772</v>
+        <v>1.008050734914647</v>
       </c>
       <c r="O17" t="n">
-        <v>-0.06136687677283041</v>
+        <v>9.370556832228718e-16</v>
       </c>
       <c r="P17" t="n">
-        <v>0.0437018000843345</v>
+        <v>-3.405458763754786e-16</v>
       </c>
       <c r="Q17" t="n">
-        <v>-34.31137713150627</v>
+        <v>2.604124554052841</v>
       </c>
       <c r="R17" t="n">
-        <v>0.00303773914465606</v>
+        <v>-5.745889693566162e-17</v>
       </c>
       <c r="S17" t="n">
-        <v>0.01449947237915819</v>
+        <v>-5.52797777969674e-17</v>
       </c>
       <c r="T17" t="n">
-        <v>0.3906989825138306</v>
+        <v>6.264432611438024e-17</v>
       </c>
       <c r="U17" t="n">
-        <v>0.5229104250473664</v>
+        <v>-3.127317241286183e-17</v>
       </c>
       <c r="V17" t="n">
-        <v>-0.01317447425773871</v>
+        <v>-2.89336625863631e-16</v>
       </c>
       <c r="W17" t="n">
-        <v>5.246722918687881</v>
+        <v>0.2278613080671951</v>
       </c>
       <c r="X17" t="n">
-        <v>-0.4784684597539604</v>
+        <v>-4.193729461825775e-16</v>
       </c>
       <c r="Y17" t="n">
-        <v>-0.06210840641123374</v>
+        <v>-2.589004403655597e-16</v>
       </c>
       <c r="Z17" t="n">
-        <v>6.133819496658405</v>
+        <v>1.098452654872702</v>
       </c>
       <c r="AA17" t="n">
-        <v>-0.6073776678783043</v>
+        <v>-2.50650741551282e-16</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>-0.1142762458081542</v>
+        <v>0.0839907492768127</v>
       </c>
       <c r="B18" t="n">
-        <v>1.720019757756524</v>
+        <v>0.1317120320487972</v>
       </c>
       <c r="C18" t="n">
-        <v>-1.472923287207341</v>
+        <v>0.2993566839521472</v>
       </c>
       <c r="D18" t="n">
-        <v>0.08298628647109868</v>
+        <v>-9.67840104559982e-16</v>
       </c>
       <c r="E18" t="n">
-        <v>-0.0400314500908914</v>
+        <v>5.316011823962526e-16</v>
       </c>
       <c r="F18" t="n">
-        <v>2.625070266818331</v>
+        <v>0.1820671608501352</v>
       </c>
       <c r="G18" t="n">
-        <v>0.0660989982664439</v>
+        <v>-6.911487966406047e-16</v>
       </c>
       <c r="H18" t="n">
-        <v>1.030240134340809</v>
+        <v>4.268651311508887e-16</v>
       </c>
       <c r="I18" t="n">
-        <v>-9.343772687516587</v>
+        <v>0.5511885150207049</v>
       </c>
       <c r="J18" t="n">
-        <v>0.06447963069279987</v>
+        <v>0.01006539857021529</v>
       </c>
       <c r="K18" t="n">
-        <v>-2.625747489057232</v>
+        <v>0.1495582194145315</v>
       </c>
       <c r="L18" t="n">
-        <v>-2.544508886912312</v>
+        <v>0.4602673838020144</v>
       </c>
       <c r="M18" t="n">
-        <v>-0.04349082956845973</v>
+        <v>8.807983829848874e-15</v>
       </c>
       <c r="N18" t="n">
-        <v>0.004846546169292075</v>
+        <v>-1.184101487146062e-15</v>
       </c>
       <c r="O18" t="n">
-        <v>3.172796873428037</v>
+        <v>0.9973798097464643</v>
       </c>
       <c r="P18" t="n">
-        <v>-0.04883889215861442</v>
+        <v>2.33661580310347e-15</v>
       </c>
       <c r="Q18" t="n">
-        <v>0.003037739144656016</v>
+        <v>-5.745889693566194e-17</v>
       </c>
       <c r="R18" t="n">
-        <v>-40.1973574258942</v>
+        <v>1.991861749471614</v>
       </c>
       <c r="S18" t="n">
-        <v>-2.791096470982241</v>
+        <v>1.94765098823494</v>
       </c>
       <c r="T18" t="n">
-        <v>-3.348814704112391</v>
+        <v>0.7712729598235979</v>
       </c>
       <c r="U18" t="n">
-        <v>-2.398552448772011</v>
+        <v>0.6534313968302583</v>
       </c>
       <c r="V18" t="n">
-        <v>0.01167666975947611</v>
+        <v>-2.776502182116074e-15</v>
       </c>
       <c r="W18" t="n">
-        <v>-0.2745368285105038</v>
+        <v>1.797342179294607e-15</v>
       </c>
       <c r="X18" t="n">
-        <v>-2.050345093121507</v>
+        <v>0.4432443759752317</v>
       </c>
       <c r="Y18" t="n">
-        <v>-0.06298459582954752</v>
+        <v>-6.169648939370136e-16</v>
       </c>
       <c r="Z18" t="n">
-        <v>-0.3800604435737475</v>
+        <v>5.407242939561736e-16</v>
       </c>
       <c r="AA18" t="n">
-        <v>1.426300544919179</v>
+        <v>1.075634948089137</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>-0.017383194982657</v>
+        <v>-0.001029452297107746</v>
       </c>
       <c r="B19" t="n">
-        <v>-0.1292743109193413</v>
+        <v>-0.1548982083665889</v>
       </c>
       <c r="C19" t="n">
-        <v>-0.5278618491030866</v>
+        <v>-0.9000752100896849</v>
       </c>
       <c r="D19" t="n">
-        <v>-0.009347721661147527</v>
+        <v>7.104945111132761e-16</v>
       </c>
       <c r="E19" t="n">
-        <v>-0.05836804347281759</v>
+        <v>-1.968867188832426e-16</v>
       </c>
       <c r="F19" t="n">
-        <v>0.09475291630663096</v>
+        <v>-0.3489153655350308</v>
       </c>
       <c r="G19" t="n">
-        <v>0.07313562604966699</v>
+        <v>2.29000447875476e-16</v>
       </c>
       <c r="H19" t="n">
-        <v>-0.002490278289474583</v>
+        <v>-8.248632120684609e-17</v>
       </c>
       <c r="I19" t="n">
-        <v>2.491636785242362</v>
+        <v>-1.934464379029403</v>
       </c>
       <c r="J19" t="n">
-        <v>0.03480377591465639</v>
+        <v>-0.00102962340408738</v>
       </c>
       <c r="K19" t="n">
-        <v>0.01980095488095185</v>
+        <v>-0.1556929556002188</v>
       </c>
       <c r="L19" t="n">
-        <v>-0.4793215894898791</v>
+        <v>-0.9068774117505555</v>
       </c>
       <c r="M19" t="n">
-        <v>0.07073476385981424</v>
+        <v>2.584785212029675e-16</v>
       </c>
       <c r="N19" t="n">
-        <v>-0.03803674285421259</v>
+        <v>5.466642736909426e-17</v>
       </c>
       <c r="O19" t="n">
-        <v>-0.1237535077874993</v>
+        <v>0.3507274610483516</v>
       </c>
       <c r="P19" t="n">
-        <v>-0.04818092515576726</v>
+        <v>1.697406369097807e-16</v>
       </c>
       <c r="Q19" t="n">
-        <v>0.01449947237915823</v>
+        <v>-5.527977779696742e-17</v>
       </c>
       <c r="R19" t="n">
-        <v>-2.791096470982242</v>
+        <v>1.94765098823494</v>
       </c>
       <c r="S19" t="n">
-        <v>26.26018535466805</v>
+        <v>-11.72849405856888</v>
       </c>
       <c r="T19" t="n">
-        <v>1.46571467014005</v>
+        <v>-2.700788669656315</v>
       </c>
       <c r="U19" t="n">
-        <v>0.4024425897349228</v>
+        <v>-2.245778386307215</v>
       </c>
       <c r="V19" t="n">
-        <v>-0.0353191329907453</v>
+        <v>8.335843405471596e-17</v>
       </c>
       <c r="W19" t="n">
-        <v>0.1238600376698312</v>
+        <v>-1.852487563144764e-17</v>
       </c>
       <c r="X19" t="n">
-        <v>0.6304805604576987</v>
+        <v>-0.0003128781032645427</v>
       </c>
       <c r="Y19" t="n">
-        <v>-0.008776952526654475</v>
+        <v>1.481301198503847e-16</v>
       </c>
       <c r="Z19" t="n">
-        <v>0.08487437172779527</v>
+        <v>4.879178447897005e-17</v>
       </c>
       <c r="AA19" t="n">
-        <v>0.01899118460169086</v>
+        <v>-0.0003756858818615209</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>-0.1123496755649706</v>
+        <v>-0.4485099892615994</v>
       </c>
       <c r="B20" t="n">
-        <v>0.9557205570893484</v>
+        <v>-0.3658659966946982</v>
       </c>
       <c r="C20" t="n">
-        <v>1.813446858373075</v>
+        <v>-0.5616049500888078</v>
       </c>
       <c r="D20" t="n">
-        <v>-0.1280226980225189</v>
+        <v>3.247762197431187e-15</v>
       </c>
       <c r="E20" t="n">
-        <v>-0.3361638313409374</v>
+        <v>-1.031565610655227e-15</v>
       </c>
       <c r="F20" t="n">
-        <v>1.32575086431029</v>
+        <v>-0.395353680116254</v>
       </c>
       <c r="G20" t="n">
-        <v>0.06837994045107865</v>
+        <v>1.484789642213299e-15</v>
       </c>
       <c r="H20" t="n">
-        <v>0.4089003556476137</v>
+        <v>-4.055425597086791e-16</v>
       </c>
       <c r="I20" t="n">
-        <v>7.785166573679936</v>
+        <v>-0.7339825201268612</v>
       </c>
       <c r="J20" t="n">
-        <v>-0.0301108637949353</v>
+        <v>-0.448902598354377</v>
       </c>
       <c r="K20" t="n">
-        <v>1.255340769714343</v>
+        <v>-0.3706875798819583</v>
       </c>
       <c r="L20" t="n">
-        <v>1.338077009442699</v>
+        <v>-0.577525469621741</v>
       </c>
       <c r="M20" t="n">
-        <v>0.1571351373104557</v>
+        <v>-1.744364857432541e-15</v>
       </c>
       <c r="N20" t="n">
-        <v>-0.4230659291664233</v>
+        <v>8.399154813701653e-16</v>
       </c>
       <c r="O20" t="n">
-        <v>-0.7960451429673908</v>
+        <v>0.4045123829044742</v>
       </c>
       <c r="P20" t="n">
-        <v>-0.1169252807846761</v>
+        <v>-3.039397228271333e-16</v>
       </c>
       <c r="Q20" t="n">
-        <v>0.3906989825138308</v>
+        <v>6.264432611438042e-17</v>
       </c>
       <c r="R20" t="n">
-        <v>-3.348814704112392</v>
+        <v>0.771272959823598</v>
       </c>
       <c r="S20" t="n">
-        <v>1.46571467014005</v>
+        <v>-2.700788669656315</v>
       </c>
       <c r="T20" t="n">
-        <v>4.397382135082048</v>
+        <v>-1.086422682238724</v>
       </c>
       <c r="U20" t="n">
-        <v>10.63464000834075</v>
+        <v>-1.124377228053689</v>
       </c>
       <c r="V20" t="n">
-        <v>0.06643720840933313</v>
+        <v>1.577677205882151e-15</v>
       </c>
       <c r="W20" t="n">
-        <v>-0.03622766620909351</v>
+        <v>-6.591128722338825e-16</v>
       </c>
       <c r="X20" t="n">
-        <v>1.643480254620338</v>
+        <v>-0.0004586971556476577</v>
       </c>
       <c r="Y20" t="n">
-        <v>-0.03989487785367306</v>
+        <v>7.947159014693963e-16</v>
       </c>
       <c r="Z20" t="n">
-        <v>-0.04188539132208546</v>
+        <v>-3.216938729515436e-16</v>
       </c>
       <c r="AA20" t="n">
-        <v>0.3997583439603225</v>
+        <v>-0.0009190270871351806</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>-0.3805858670024376</v>
+        <v>-0.8853326186362753</v>
       </c>
       <c r="B21" t="n">
-        <v>2.611995783481038</v>
+        <v>-0.3751695949649373</v>
       </c>
       <c r="C21" t="n">
-        <v>0.9339292753502983</v>
+        <v>-0.5080359459677226</v>
       </c>
       <c r="D21" t="n">
-        <v>-0.06995697083609853</v>
+        <v>1.454720075916617e-15</v>
       </c>
       <c r="E21" t="n">
-        <v>-0.1414267378950517</v>
+        <v>-3.915137501783901e-16</v>
       </c>
       <c r="F21" t="n">
-        <v>3.184195409819672</v>
+        <v>-0.2966997846548376</v>
       </c>
       <c r="G21" t="n">
-        <v>0.1410476084206084</v>
+        <v>5.945945227135952e-16</v>
       </c>
       <c r="H21" t="n">
-        <v>0.4523065077777615</v>
+        <v>-1.246074753346389e-16</v>
       </c>
       <c r="I21" t="n">
-        <v>6.813390689025392</v>
+        <v>-0.621945962018902</v>
       </c>
       <c r="J21" t="n">
-        <v>-0.283601389041076</v>
+        <v>-0.8860804614575661</v>
       </c>
       <c r="K21" t="n">
-        <v>2.69704787187172</v>
+        <v>-0.380439774504827</v>
       </c>
       <c r="L21" t="n">
-        <v>0.6268489586541659</v>
+        <v>-0.5216323966291418</v>
       </c>
       <c r="M21" t="n">
-        <v>0.2658634213724857</v>
+        <v>-1.023035054805021e-15</v>
       </c>
       <c r="N21" t="n">
-        <v>0.03332009187427502</v>
+        <v>3.427854697205195e-16</v>
       </c>
       <c r="O21" t="n">
-        <v>-1.899240216894777</v>
+        <v>0.3048297340942762</v>
       </c>
       <c r="P21" t="n">
-        <v>-0.171367625673485</v>
+        <v>-2.52006390082351e-16</v>
       </c>
       <c r="Q21" t="n">
-        <v>0.522910425047366</v>
+        <v>-3.127317241286176e-17</v>
       </c>
       <c r="R21" t="n">
-        <v>-2.398552448772013</v>
+        <v>0.6534313968302583</v>
       </c>
       <c r="S21" t="n">
-        <v>0.402442589734923</v>
+        <v>-2.245778386307215</v>
       </c>
       <c r="T21" t="n">
-        <v>10.63464000834075</v>
+        <v>-1.12437722805369</v>
       </c>
       <c r="U21" t="n">
-        <v>9.081843250266715</v>
+        <v>-0.9766534892225625</v>
       </c>
       <c r="V21" t="n">
-        <v>-0.05527267590342473</v>
+        <v>5.962608962404225e-16</v>
       </c>
       <c r="W21" t="n">
-        <v>0.07140308902449477</v>
+        <v>-2.575774846534283e-16</v>
       </c>
       <c r="X21" t="n">
-        <v>0.632699305493247</v>
+        <v>-0.0003555602966187011</v>
       </c>
       <c r="Y21" t="n">
-        <v>-0.1035524945935813</v>
+        <v>2.753808411011512e-16</v>
       </c>
       <c r="Z21" t="n">
-        <v>0.09601505712293779</v>
+        <v>-1.657679104178384e-16</v>
       </c>
       <c r="AA21" t="n">
-        <v>0.7235894062812651</v>
+        <v>-0.0008229058200309764</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>-0.09857334360723925</v>
+        <v>-4.44013549193938e-17</v>
       </c>
       <c r="B22" t="n">
-        <v>0.8434180300837161</v>
+        <v>6.482093157361339e-16</v>
       </c>
       <c r="C22" t="n">
-        <v>-0.6841530643549898</v>
+        <v>4.626781688552997e-16</v>
       </c>
       <c r="D22" t="n">
-        <v>-1.623444508206282</v>
+        <v>-0.02193799092565492</v>
       </c>
       <c r="E22" t="n">
-        <v>-0.2624065950466219</v>
+        <v>-2.389715389611256e-15</v>
       </c>
       <c r="F22" t="n">
-        <v>-0.3459967911920073</v>
+        <v>-2.841520316624998e-15</v>
       </c>
       <c r="G22" t="n">
-        <v>5.337001681798523</v>
+        <v>0.1711169882755983</v>
       </c>
       <c r="H22" t="n">
-        <v>-0.08356384241569548</v>
+        <v>-1.317828186369678e-15</v>
       </c>
       <c r="I22" t="n">
-        <v>-0.4473322690239473</v>
+        <v>-8.62461831101012e-16</v>
       </c>
       <c r="J22" t="n">
-        <v>0.1161924861022333</v>
+        <v>2.834107188960352e-16</v>
       </c>
       <c r="K22" t="n">
-        <v>-0.4836004603135647</v>
+        <v>-2.505227853843419e-15</v>
       </c>
       <c r="L22" t="n">
-        <v>0.02808600165576949</v>
+        <v>-1.104870210227162e-15</v>
       </c>
       <c r="M22" t="n">
-        <v>-1.693080574389559</v>
+        <v>-0.01792151295006113</v>
       </c>
       <c r="N22" t="n">
-        <v>0.2443410447201789</v>
+        <v>2.703582589645091e-16</v>
       </c>
       <c r="O22" t="n">
-        <v>-0.00655300568869692</v>
+        <v>-5.407272537082233e-15</v>
       </c>
       <c r="P22" t="n">
-        <v>5.252382510381475</v>
+        <v>0.2279949242537498</v>
       </c>
       <c r="Q22" t="n">
-        <v>-0.0131744742577387</v>
+        <v>-2.89336625863631e-16</v>
       </c>
       <c r="R22" t="n">
-        <v>0.01167666975947614</v>
+        <v>-2.776502182116074e-15</v>
       </c>
       <c r="S22" t="n">
-        <v>-0.03531913299074526</v>
+        <v>8.3358434054716e-17</v>
       </c>
       <c r="T22" t="n">
-        <v>0.06643720840933311</v>
+        <v>1.577677205882151e-15</v>
       </c>
       <c r="U22" t="n">
-        <v>-0.05527267590342473</v>
+        <v>5.962608962404231e-16</v>
       </c>
       <c r="V22" t="n">
-        <v>56.04712953440184</v>
+        <v>1.469063767857263</v>
       </c>
       <c r="W22" t="n">
-        <v>-0.08803258970993719</v>
+        <v>-1.983105333258997e-15</v>
       </c>
       <c r="X22" t="n">
-        <v>-0.06278619231606697</v>
+        <v>4.843109055072023e-15</v>
       </c>
       <c r="Y22" t="n">
-        <v>4.970599659378523</v>
+        <v>0.7132723078243008</v>
       </c>
       <c r="Z22" t="n">
-        <v>-0.01348713155686793</v>
+        <v>-1.08747658376026e-15</v>
       </c>
       <c r="AA22" t="n">
-        <v>-0.3154825939227565</v>
+        <v>2.131243306990414e-16</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>-0.1340388185222632</v>
+        <v>1.162737942979771e-17</v>
       </c>
       <c r="B23" t="n">
-        <v>0.1356721416658286</v>
+        <v>-5.768805169174933e-16</v>
       </c>
       <c r="C23" t="n">
-        <v>0.4648977372355639</v>
+        <v>-3.527770665191417e-16</v>
       </c>
       <c r="D23" t="n">
-        <v>0.07497279927591531</v>
+        <v>-2.427842827781269e-15</v>
       </c>
       <c r="E23" t="n">
-        <v>-2.065486994334228</v>
+        <v>-0.003817359570537388</v>
       </c>
       <c r="F23" t="n">
-        <v>0.4195138051584592</v>
+        <v>2.128233177967782e-15</v>
       </c>
       <c r="G23" t="n">
-        <v>0.02977567495134125</v>
+        <v>-1.1538811284587e-15</v>
       </c>
       <c r="H23" t="n">
-        <v>5.231435240104406</v>
+        <v>0.1709153137206992</v>
       </c>
       <c r="I23" t="n">
-        <v>0.3863315273073227</v>
+        <v>8.573543836146655e-16</v>
       </c>
       <c r="J23" t="n">
-        <v>0.1936123998028958</v>
+        <v>-2.055058311315416e-16</v>
       </c>
       <c r="K23" t="n">
-        <v>-0.6745133220491555</v>
+        <v>1.304562247575277e-15</v>
       </c>
       <c r="L23" t="n">
-        <v>0.1271902983050405</v>
+        <v>5.160023992588325e-16</v>
       </c>
       <c r="M23" t="n">
-        <v>-0.2170838249720594</v>
+        <v>-2.55243170737166e-15</v>
       </c>
       <c r="N23" t="n">
-        <v>-1.833428106827623</v>
+        <v>0.0001944904163663913</v>
       </c>
       <c r="O23" t="n">
-        <v>-0.4094931920805068</v>
+        <v>3.768807854567631e-15</v>
       </c>
       <c r="P23" t="n">
-        <v>-0.108035871604333</v>
+        <v>-1.313533409624754e-15</v>
       </c>
       <c r="Q23" t="n">
-        <v>5.246722918687881</v>
+        <v>0.2278613080671951</v>
       </c>
       <c r="R23" t="n">
-        <v>-0.274536828510504</v>
+        <v>1.797342179294607e-15</v>
       </c>
       <c r="S23" t="n">
-        <v>0.1238600376698312</v>
+        <v>-1.852487563144756e-17</v>
       </c>
       <c r="T23" t="n">
-        <v>-0.03622766620909344</v>
+        <v>-6.591128722338826e-16</v>
       </c>
       <c r="U23" t="n">
-        <v>0.07140308902449477</v>
+        <v>-2.575774846534275e-16</v>
       </c>
       <c r="V23" t="n">
-        <v>-0.08803258970993716</v>
+        <v>-1.983105333258997e-15</v>
       </c>
       <c r="W23" t="n">
-        <v>56.11185665843034</v>
+        <v>1.467035473076147</v>
       </c>
       <c r="X23" t="n">
-        <v>-0.03535821993102417</v>
+        <v>-2.868931943944592e-15</v>
       </c>
       <c r="Y23" t="n">
-        <v>-0.05356941604812628</v>
+        <v>-1.303241390500077e-15</v>
       </c>
       <c r="Z23" t="n">
-        <v>5.081436951657831</v>
+        <v>0.7145740187056362</v>
       </c>
       <c r="AA23" t="n">
-        <v>0.09259653551755159</v>
+        <v>2.855469892785458e-16</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>1.641268049482536</v>
+        <v>0.8781866342360253</v>
       </c>
       <c r="B24" t="n">
-        <v>-2.951629545768504</v>
+        <v>0.4138087580895909</v>
       </c>
       <c r="C24" t="n">
-        <v>-4.872338936969924</v>
+        <v>0.3427257700439811</v>
       </c>
       <c r="D24" t="n">
-        <v>-0.04652939776438733</v>
+        <v>-8.394861729787418e-15</v>
       </c>
       <c r="E24" t="n">
-        <v>-0.6532567243171629</v>
+        <v>3.591005271356497e-15</v>
       </c>
       <c r="F24" t="n">
-        <v>-0.4803561888961823</v>
+        <v>0.541484987428966</v>
       </c>
       <c r="G24" t="n">
-        <v>-0.03693212479203903</v>
+        <v>-2.481828301047755e-15</v>
       </c>
       <c r="H24" t="n">
-        <v>0.2853037065911367</v>
+        <v>8.898295177029082e-16</v>
       </c>
       <c r="I24" t="n">
-        <v>-2.698014891868741</v>
+        <v>0.3870988161753057</v>
       </c>
       <c r="J24" t="n">
-        <v>-1.561927866384081</v>
+        <v>-0.8789230654611183</v>
       </c>
       <c r="K24" t="n">
-        <v>2.226334790996347</v>
+        <v>-0.4186609515153872</v>
       </c>
       <c r="L24" t="n">
-        <v>5.80771766903339</v>
+        <v>-0.3380487766738055</v>
       </c>
       <c r="M24" t="n">
-        <v>0.4431876117659876</v>
+        <v>5.121282968712055e-15</v>
       </c>
       <c r="N24" t="n">
-        <v>-0.4495950769629765</v>
+        <v>5.426631478700658e-16</v>
       </c>
       <c r="O24" t="n">
-        <v>1.746614109458258</v>
+        <v>0.5585835805140056</v>
       </c>
       <c r="P24" t="n">
-        <v>0.4499433205242609</v>
+        <v>2.899685644282148e-15</v>
       </c>
       <c r="Q24" t="n">
-        <v>-0.4784684597539604</v>
+        <v>-4.193729461825782e-16</v>
       </c>
       <c r="R24" t="n">
-        <v>-2.050345093121508</v>
+        <v>0.4432443759752318</v>
       </c>
       <c r="S24" t="n">
-        <v>0.6304805604576986</v>
+        <v>-0.0003128781032645214</v>
       </c>
       <c r="T24" t="n">
-        <v>1.643480254620339</v>
+        <v>-0.000458697155647732</v>
       </c>
       <c r="U24" t="n">
-        <v>0.6326993054932475</v>
+        <v>-0.0003555602966186543</v>
       </c>
       <c r="V24" t="n">
-        <v>-0.06278619231606691</v>
+        <v>4.843109055072024e-15</v>
       </c>
       <c r="W24" t="n">
-        <v>-0.03535821993102428</v>
+        <v>-2.868931943944592e-15</v>
       </c>
       <c r="X24" t="n">
-        <v>68.31520287189196</v>
+        <v>0.8927285848985158</v>
       </c>
       <c r="Y24" t="n">
-        <v>0.09418716433261423</v>
+        <v>1.348299429760757e-15</v>
       </c>
       <c r="Z24" t="n">
-        <v>-0.01495289493199825</v>
+        <v>-3.035911428167399e-16</v>
       </c>
       <c r="AA24" t="n">
-        <v>7.274210429313568</v>
+        <v>0.2944313003526839</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>0.0561435912350044</v>
+        <v>-2.239209142907611e-17</v>
       </c>
       <c r="B25" t="n">
-        <v>0.08099713667798122</v>
+        <v>-3.112702011111814e-16</v>
       </c>
       <c r="C25" t="n">
-        <v>-0.1855838638663503</v>
+        <v>-6.783164846643296e-17</v>
       </c>
       <c r="D25" t="n">
-        <v>-6.885975186475961</v>
+        <v>0.1549630947267703</v>
       </c>
       <c r="E25" t="n">
-        <v>-0.3124212471220639</v>
+        <v>-8.176479522531828e-16</v>
       </c>
       <c r="F25" t="n">
-        <v>-0.3714016524683517</v>
+        <v>-1.96616256076576e-15</v>
       </c>
       <c r="G25" t="n">
-        <v>6.486221894468955</v>
+        <v>0.9741593419645682</v>
       </c>
       <c r="H25" t="n">
-        <v>-0.1362071837957134</v>
+        <v>-6.250833465720374e-16</v>
       </c>
       <c r="I25" t="n">
-        <v>-0.4430089848808493</v>
+        <v>-4.02154632140404e-16</v>
       </c>
       <c r="J25" t="n">
-        <v>-0.109882567019687</v>
+        <v>8.487132748131893e-17</v>
       </c>
       <c r="K25" t="n">
-        <v>-0.1188825976930062</v>
+        <v>-6.381718564684422e-16</v>
       </c>
       <c r="L25" t="n">
-        <v>-0.0003867658997993573</v>
+        <v>-2.415735709852932e-16</v>
       </c>
       <c r="M25" t="n">
-        <v>-7.003061544246973</v>
+        <v>0.1614379705728501</v>
       </c>
       <c r="N25" t="n">
-        <v>0.1733919514998904</v>
+        <v>1.815542495463897e-16</v>
       </c>
       <c r="O25" t="n">
-        <v>-0.1821002273832633</v>
+        <v>-1.675945387654657e-15</v>
       </c>
       <c r="P25" t="n">
-        <v>6.123235008855699</v>
+        <v>1.098524600347202</v>
       </c>
       <c r="Q25" t="n">
-        <v>-0.0621084064112337</v>
+        <v>-2.589004403655596e-16</v>
       </c>
       <c r="R25" t="n">
-        <v>-0.06298459582954752</v>
+        <v>-6.169648939370138e-16</v>
       </c>
       <c r="S25" t="n">
-        <v>-0.008776952526654482</v>
+        <v>1.481301198503846e-16</v>
       </c>
       <c r="T25" t="n">
-        <v>-0.0398948778536731</v>
+        <v>7.947159014693963e-16</v>
       </c>
       <c r="U25" t="n">
-        <v>-0.1035524945935813</v>
+        <v>2.753808411011504e-16</v>
       </c>
       <c r="V25" t="n">
-        <v>4.970599659378523</v>
+        <v>0.7132723078243008</v>
       </c>
       <c r="W25" t="n">
-        <v>-0.05356941604812628</v>
+        <v>-1.303241390500077e-15</v>
       </c>
       <c r="X25" t="n">
-        <v>0.09418716433261423</v>
+        <v>1.348299429760757e-15</v>
       </c>
       <c r="Y25" t="n">
-        <v>-1.177271228732117</v>
+        <v>2.145096811933809</v>
       </c>
       <c r="Z25" t="n">
-        <v>-0.02902248536181955</v>
+        <v>-6.692991632766927e-16</v>
       </c>
       <c r="AA25" t="n">
-        <v>-0.09353547539926588</v>
+        <v>3.203358204517286e-16</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>0.02060803788629979</v>
+        <v>-2.803191920560953e-17</v>
       </c>
       <c r="B26" t="n">
-        <v>0.0842715549067401</v>
+        <v>6.353841898545101e-17</v>
       </c>
       <c r="C26" t="n">
-        <v>0.1735964690947602</v>
+        <v>-3.557803605218277e-17</v>
       </c>
       <c r="D26" t="n">
-        <v>0.1130759083614428</v>
+        <v>-1.087915168824748e-15</v>
       </c>
       <c r="E26" t="n">
-        <v>-7.209653834568223</v>
+        <v>0.2045401213949267</v>
       </c>
       <c r="F26" t="n">
-        <v>0.1702980696093798</v>
+        <v>1.086164613536816e-15</v>
       </c>
       <c r="G26" t="n">
-        <v>0.007874901825735955</v>
+        <v>-5.107206273553864e-16</v>
       </c>
       <c r="H26" t="n">
-        <v>6.630293134008576</v>
+        <v>0.9740993718618542</v>
       </c>
       <c r="I26" t="n">
-        <v>0.5422915964793458</v>
+        <v>3.45020851695141e-16</v>
       </c>
       <c r="J26" t="n">
-        <v>0.0119223638096283</v>
+        <v>-6.023827293227169e-17</v>
       </c>
       <c r="K26" t="n">
-        <v>-0.3757052065289835</v>
+        <v>-6.491623686141018e-18</v>
       </c>
       <c r="L26" t="n">
-        <v>-0.04394511397550993</v>
+        <v>-1.367594521940173e-16</v>
       </c>
       <c r="M26" t="n">
-        <v>-0.3368017147838948</v>
+        <v>-1.13672222582041e-15</v>
       </c>
       <c r="N26" t="n">
-        <v>-7.229748159878575</v>
+        <v>0.2110164439067542</v>
       </c>
       <c r="O26" t="n">
-        <v>-0.3732416647863951</v>
+        <v>1.490196332373673e-15</v>
       </c>
       <c r="P26" t="n">
-        <v>-0.1272072262122085</v>
+        <v>-6.524779255080971e-16</v>
       </c>
       <c r="Q26" t="n">
-        <v>6.133819496658405</v>
+        <v>1.098452654872702</v>
       </c>
       <c r="R26" t="n">
-        <v>-0.3800604435737476</v>
+        <v>5.407242939561742e-16</v>
       </c>
       <c r="S26" t="n">
-        <v>0.08487437172779527</v>
+        <v>4.879178447897001e-17</v>
       </c>
       <c r="T26" t="n">
-        <v>-0.04188539132208542</v>
+        <v>-3.216938729515429e-16</v>
       </c>
       <c r="U26" t="n">
-        <v>0.09601505712293798</v>
+        <v>-1.657679104178378e-16</v>
       </c>
       <c r="V26" t="n">
-        <v>-0.01348713155686793</v>
+        <v>-1.08747658376026e-15</v>
       </c>
       <c r="W26" t="n">
-        <v>5.081436951657831</v>
+        <v>0.7145740187056363</v>
       </c>
       <c r="X26" t="n">
-        <v>-0.01495289493199831</v>
+        <v>-3.035911428167392e-16</v>
       </c>
       <c r="Y26" t="n">
-        <v>-0.02902248536181959</v>
+        <v>-6.692991632766925e-16</v>
       </c>
       <c r="Z26" t="n">
-        <v>-0.9616958051419022</v>
+        <v>2.145096811933808</v>
       </c>
       <c r="AA26" t="n">
-        <v>0.03303747235367893</v>
+        <v>1.275729039235028e-16</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>0.3688964258186498</v>
+        <v>1.545025963891932</v>
       </c>
       <c r="B27" t="n">
-        <v>-3.694736014862674</v>
+        <v>0.3946494718763033</v>
       </c>
       <c r="C27" t="n">
-        <v>-3.128439198956057</v>
+        <v>0.2305570657281349</v>
       </c>
       <c r="D27" t="n">
-        <v>-0.1399306999868982</v>
+        <v>-3.288546787631618e-15</v>
       </c>
       <c r="E27" t="n">
-        <v>-0.4416675868065112</v>
+        <v>2.376062801743565e-15</v>
       </c>
       <c r="F27" t="n">
-        <v>0.93655038481588</v>
+        <v>0.5296515517432172</v>
       </c>
       <c r="G27" t="n">
-        <v>-0.1543253050336538</v>
+        <v>-7.422117542355817e-16</v>
       </c>
       <c r="H27" t="n">
-        <v>0.9842143876026266</v>
+        <v>8.549083270317698e-16</v>
       </c>
       <c r="I27" t="n">
-        <v>-1.991259003350293</v>
+        <v>0.9272706486401135</v>
       </c>
       <c r="J27" t="n">
-        <v>-0.03876353897098994</v>
+        <v>-1.546277333727295</v>
       </c>
       <c r="K27" t="n">
-        <v>3.367259288612125</v>
+        <v>-0.3995492601013799</v>
       </c>
       <c r="L27" t="n">
-        <v>3.6049805151116</v>
+        <v>-0.2302815346541635</v>
       </c>
       <c r="M27" t="n">
-        <v>0.01935864227917941</v>
+        <v>4.911085003080613e-15</v>
       </c>
       <c r="N27" t="n">
-        <v>-0.1790713917819428</v>
+        <v>-4.463615971472975e-16</v>
       </c>
       <c r="O27" t="n">
-        <v>2.385010128216951</v>
+        <v>0.5479858710481769</v>
       </c>
       <c r="P27" t="n">
-        <v>0.5604429974200316</v>
+        <v>1.798254687057366e-15</v>
       </c>
       <c r="Q27" t="n">
-        <v>-0.6073776678783045</v>
+        <v>-2.506507415512819e-16</v>
       </c>
       <c r="R27" t="n">
-        <v>1.42630054491918</v>
+        <v>1.075634948089137</v>
       </c>
       <c r="S27" t="n">
-        <v>0.01899118460169084</v>
+        <v>-0.0003756858818614959</v>
       </c>
       <c r="T27" t="n">
-        <v>0.3997583439603228</v>
+        <v>-0.0009190270871351553</v>
       </c>
       <c r="U27" t="n">
-        <v>0.7235894062812644</v>
+        <v>-0.00082290582003107</v>
       </c>
       <c r="V27" t="n">
-        <v>-0.3154825939227567</v>
+        <v>2.131243306990419e-16</v>
       </c>
       <c r="W27" t="n">
-        <v>0.09259653551755176</v>
+        <v>2.855469892785469e-16</v>
       </c>
       <c r="X27" t="n">
-        <v>7.274210429313566</v>
+        <v>0.2944313003526839</v>
       </c>
       <c r="Y27" t="n">
-        <v>-0.09353547539926588</v>
+        <v>3.203358204517297e-16</v>
       </c>
       <c r="Z27" t="n">
-        <v>0.03303747235367893</v>
+        <v>1.275729039235027e-16</v>
       </c>
       <c r="AA27" t="n">
-        <v>-0.7372806724476533</v>
+        <v>1.655402570095338</v>
       </c>
     </row>
   </sheetData>
